--- a/inspection_forms/040_data_center_inspection_form--inspection_forms.xlsx
+++ b/inspection_forms/040_data_center_inspection_form--inspection_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -872,8 +872,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
-    <col width="49" customWidth="1" min="2" max="2"/>
-    <col width="49" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -935,12 +935,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'critical',_'value':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'critical', 'value': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'non_critical',_'value':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'non_critical', 'value': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'unknown',_'value':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'unknown', 'value': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'working',_'value':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'working', 'value': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'not_working',_'value':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'not_working', 'value': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'not_applicable',_'value':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'not_applicable', 'value': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'up_to_date',_'value':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'up_to_date', 'value': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'not_up_to_date',_'value':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'not_up_to_date', 'value': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1105,12 +1105,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true,_'value':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True, 'value': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false,_'value':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False, 'value': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'not_applicable',_'value':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'not_applicable', 'value': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true,_'value':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True, 'value': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false,_'value':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False, 'value': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'not_applicable',_'value':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'not_applicable', 'value': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true,_'value':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True, 'value': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false,_'value':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False, 'value': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1241,12 +1241,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'not_applicable',_'value':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'not_applicable', 'value': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true,_'value':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True, 'value': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1275,12 +1275,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false,_'value':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False, 'value': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1292,12 +1292,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'not_applicable',_'value':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'not_applicable', 'value': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1309,12 +1309,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true,_'value':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True, 'value': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false,_'value':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False, 'value': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1343,12 +1343,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'not_applicable',_'value':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'not_applicable', 'value': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
